--- a/AAII_Financials/Yearly/PG_YR_FIN.xlsx
+++ b/AAII_Financials/Yearly/PG_YR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="115" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="117" uniqueCount="92">
   <si>
     <t>PG</t>
   </si>
@@ -656,219 +656,231 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:R102"/>
+  <dimension ref="A5:S102"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="4.42578125" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="17" width="16" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="18" width="16" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:19" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:19" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>46203</v>
+      </c>
+      <c r="E7" s="2">
         <v>45838</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45473</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45107</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>44742</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>44377</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>44012</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>43646</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>43281</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>42916</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>42551</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>42185</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>41820</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>41455</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>41090</v>
       </c>
-      <c r="R7" s="2"/>
-    </row>
-    <row r="8" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="S7" s="2"/>
+    </row>
+    <row r="8" spans="1:19" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
+        <v>87032000</v>
+      </c>
+      <c r="E8" s="3">
         <v>84284000</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>84039000</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>82006000</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>80187000</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>76118000</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>70950000</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>67684000</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>66832000</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>65058000</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>65299000</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>70749000</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>74401000</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>80116000</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="R8" s="3">
         <v>83680000</v>
       </c>
-      <c r="R8" s="3"/>
-    </row>
-    <row r="9" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="S8" s="3"/>
+    </row>
+    <row r="9" spans="1:19" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D9" s="3">
+        <v>42756000</v>
+      </c>
+      <c r="E9" s="3">
         <v>41014000</v>
       </c>
-      <c r="E9" s="3">
-        <v>40600000</v>
-      </c>
       <c r="F9" s="3">
+        <v>40848000</v>
+      </c>
+      <c r="G9" s="3">
         <v>42760000</v>
       </c>
-      <c r="G9" s="3">
+      <c r="H9" s="3">
         <v>42157000</v>
       </c>
-      <c r="H9" s="3">
+      <c r="I9" s="3">
         <v>37108000</v>
       </c>
-      <c r="I9" s="3">
+      <c r="J9" s="3">
         <v>35250000</v>
       </c>
-      <c r="J9" s="3">
+      <c r="K9" s="3">
         <v>34768000</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>34432000</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <v>31942000</v>
       </c>
-      <c r="M9" s="3">
+      <c r="N9" s="3">
         <v>32191000</v>
       </c>
-      <c r="N9" s="3">
+      <c r="O9" s="3">
         <v>36442000</v>
       </c>
-      <c r="O9" s="3">
+      <c r="P9" s="3">
         <v>79641000</v>
       </c>
-      <c r="P9" s="3">
+      <c r="Q9" s="3">
         <v>81028000</v>
       </c>
-      <c r="Q9" s="3">
+      <c r="R9" s="3">
         <v>42391000</v>
       </c>
-      <c r="R9" s="3"/>
-    </row>
-    <row r="10" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="S9" s="3"/>
+    </row>
+    <row r="10" spans="1:19" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D10" s="3">
+        <v>44276000</v>
+      </c>
+      <c r="E10" s="3">
         <v>43270000</v>
       </c>
-      <c r="E10" s="3">
-        <v>43439000</v>
-      </c>
       <c r="F10" s="3">
+        <v>43191000</v>
+      </c>
+      <c r="G10" s="3">
         <v>39246000</v>
       </c>
-      <c r="G10" s="3">
+      <c r="H10" s="3">
         <v>38030000</v>
       </c>
-      <c r="H10" s="3">
+      <c r="I10" s="3">
         <v>39010000</v>
       </c>
-      <c r="I10" s="3">
+      <c r="J10" s="3">
         <v>35700000</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>32916000</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>32400000</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>33116000</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>33108000</v>
       </c>
-      <c r="N10" s="3">
+      <c r="O10" s="3">
         <v>34307000</v>
       </c>
-      <c r="O10" s="3">
+      <c r="P10" s="3">
         <v>-5240000</v>
       </c>
-      <c r="P10" s="3">
+      <c r="Q10" s="3">
         <v>-912000</v>
       </c>
-      <c r="Q10" s="3">
+      <c r="R10" s="3">
         <v>41289000</v>
       </c>
-      <c r="R10" s="3"/>
-    </row>
-    <row r="11" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="S10" s="3"/>
+    </row>
+    <row r="11" spans="1:19" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>6</v>
       </c>
@@ -887,8 +899,9 @@
       <c r="P11" s="3"/>
       <c r="Q11" s="3"/>
       <c r="R11" s="3"/>
-    </row>
-    <row r="12" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="S11" s="3"/>
+    </row>
+    <row r="12" spans="1:19" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>7</v>
       </c>
@@ -896,7 +909,7 @@
         <v>2100000</v>
       </c>
       <c r="E12" s="3">
-        <v>2000000</v>
+        <v>2100000</v>
       </c>
       <c r="F12" s="3">
         <v>2000000</v>
@@ -905,19 +918,19 @@
         <v>2000000</v>
       </c>
       <c r="H12" s="3">
+        <v>2000000</v>
+      </c>
+      <c r="I12" s="3">
         <v>1900000</v>
       </c>
-      <c r="I12" s="3">
+      <c r="J12" s="3">
         <v>1800000</v>
       </c>
-      <c r="J12" s="3">
+      <c r="K12" s="3">
         <v>1900000</v>
       </c>
-      <c r="K12" s="3">
+      <c r="L12" s="3">
         <v>1908000</v>
-      </c>
-      <c r="L12" s="3" t="s">
-        <v>8</v>
       </c>
       <c r="M12" s="3" t="s">
         <v>8</v>
@@ -931,12 +944,15 @@
       <c r="P12" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="Q12" s="3">
+      <c r="Q12" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="R12" s="3">
         <v>1982000</v>
       </c>
-      <c r="R12" s="3"/>
-    </row>
-    <row r="13" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="S12" s="3"/>
+    </row>
+    <row r="13" spans="1:19" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -982,87 +998,93 @@
       <c r="Q13" s="3">
         <v>0</v>
       </c>
-      <c r="R13" s="3"/>
-    </row>
-    <row r="14" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="R13" s="3">
+        <v>0</v>
+      </c>
+      <c r="S13" s="3"/>
+    </row>
+    <row r="14" spans="1:19" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D14" s="3">
+        <v>1255000</v>
+      </c>
+      <c r="E14" s="3">
         <v>1119000</v>
       </c>
-      <c r="E14" s="3">
-        <v>2006000</v>
-      </c>
       <c r="F14" s="3">
+        <v>1348000</v>
+      </c>
+      <c r="G14" s="3">
         <v>9000</v>
       </c>
-      <c r="G14" s="3">
+      <c r="H14" s="3">
         <v>5000</v>
       </c>
-      <c r="H14" s="3">
+      <c r="I14" s="3">
         <v>19000</v>
       </c>
-      <c r="I14" s="3">
+      <c r="J14" s="3">
         <v>13000</v>
       </c>
-      <c r="J14" s="3">
+      <c r="K14" s="3">
         <v>8366000</v>
       </c>
-      <c r="K14" s="3">
+      <c r="L14" s="3">
         <v>-161000</v>
       </c>
-      <c r="L14" s="3">
+      <c r="M14" s="3">
         <v>730000</v>
       </c>
-      <c r="M14" s="3">
+      <c r="N14" s="3">
         <v>920000</v>
       </c>
-      <c r="N14" s="3">
+      <c r="O14" s="3">
         <v>2980000</v>
       </c>
-      <c r="O14" s="3">
+      <c r="P14" s="3">
         <v>757000</v>
       </c>
-      <c r="P14" s="3">
+      <c r="Q14" s="3">
         <v>1253000</v>
       </c>
-      <c r="Q14" s="3">
+      <c r="R14" s="3">
         <v>2628000</v>
       </c>
-      <c r="R14" s="3"/>
-    </row>
-    <row r="15" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="S14" s="3"/>
+    </row>
+    <row r="15" spans="1:19" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D15" s="3">
+        <v>3160000</v>
+      </c>
+      <c r="E15" s="3">
         <v>2847000</v>
       </c>
-      <c r="E15" s="3">
+      <c r="F15" s="3">
         <v>2896000</v>
       </c>
-      <c r="F15" s="3">
+      <c r="G15" s="3">
         <v>2714000</v>
       </c>
-      <c r="G15" s="3">
+      <c r="H15" s="3">
         <v>2807000</v>
       </c>
-      <c r="H15" s="3">
+      <c r="I15" s="3">
         <v>2735000</v>
       </c>
-      <c r="I15" s="3">
+      <c r="J15" s="3">
         <v>3013000</v>
       </c>
-      <c r="J15" s="3">
+      <c r="K15" s="3">
         <v>2824000</v>
       </c>
-      <c r="K15" s="3">
+      <c r="L15" s="3">
         <v>2834000</v>
       </c>
-      <c r="L15" s="3">
-        <v>0</v>
-      </c>
       <c r="M15" s="3">
         <v>0</v>
       </c>
@@ -1078,9 +1100,12 @@
       <c r="Q15" s="3">
         <v>0</v>
       </c>
-      <c r="R15" s="3"/>
-    </row>
-    <row r="16" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="R15" s="3">
+        <v>0</v>
+      </c>
+      <c r="S15" s="3"/>
+    </row>
+    <row r="16" spans="1:19" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1096,104 +1121,111 @@
       <c r="P16" s="3"/>
       <c r="Q16" s="3"/>
       <c r="R16" s="3"/>
-    </row>
-    <row r="17" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S16" s="3"/>
+    </row>
+    <row r="17" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>65440000</v>
+      </c>
+      <c r="E17" s="3">
         <v>62676000</v>
       </c>
-      <c r="E17" s="3">
-        <v>63091000</v>
-      </c>
       <c r="F17" s="3">
+        <v>63494000</v>
+      </c>
+      <c r="G17" s="3">
         <v>63269000</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>61742000</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>57635000</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>54847000</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>53477000</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>53143000</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>51103000</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>51858000</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>59700000</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>60491000</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>66299000</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>70388000</v>
       </c>
-      <c r="R17" s="3"/>
-    </row>
-    <row r="18" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S17" s="3"/>
+    </row>
+    <row r="18" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>21592000</v>
+      </c>
+      <c r="E18" s="3">
         <v>21608000</v>
       </c>
-      <c r="E18" s="3">
-        <v>20948000</v>
-      </c>
       <c r="F18" s="3">
+        <v>20545000</v>
+      </c>
+      <c r="G18" s="3">
         <v>18737000</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>18445000</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>18483000</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>16103000</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>14207000</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>13689000</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>13955000</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>13441000</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>11049000</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>13910000</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>13817000</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>13292000</v>
       </c>
-      <c r="R18" s="3"/>
-    </row>
-    <row r="19" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S18" s="3"/>
+    </row>
+    <row r="19" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1212,248 +1244,264 @@
       <c r="P19" s="3"/>
       <c r="Q19" s="3"/>
       <c r="R19" s="3"/>
-    </row>
-    <row r="20" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S19" s="3"/>
+    </row>
+    <row r="20" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
+        <v>-487000</v>
+      </c>
+      <c r="E20" s="3">
         <v>-116000</v>
       </c>
-      <c r="E20" s="3">
-        <v>-271000</v>
-      </c>
       <c r="F20" s="3">
+        <v>-16000</v>
+      </c>
+      <c r="G20" s="3">
         <v>-74000</v>
       </c>
-      <c r="G20" s="3">
+      <c r="H20" s="3">
         <v>57000</v>
       </c>
-      <c r="H20" s="3">
+      <c r="I20" s="3">
         <v>392000</v>
       </c>
-      <c r="I20" s="3">
+      <c r="J20" s="3">
         <v>-54000</v>
       </c>
-      <c r="J20" s="3">
+      <c r="K20" s="3">
         <v>-517000</v>
       </c>
-      <c r="K20" s="3">
+      <c r="L20" s="3">
         <v>265000</v>
       </c>
-      <c r="L20" s="3">
+      <c r="M20" s="3">
         <v>-233000</v>
       </c>
-      <c r="M20" s="3">
+      <c r="N20" s="3">
         <v>507000</v>
       </c>
-      <c r="N20" s="3">
+      <c r="O20" s="3">
         <v>589000</v>
       </c>
-      <c r="O20" s="3">
+      <c r="P20" s="3">
         <v>308000</v>
       </c>
-      <c r="P20" s="3">
+      <c r="Q20" s="3">
         <v>1696000</v>
       </c>
-      <c r="Q20" s="3">
+      <c r="R20" s="3">
         <v>262000</v>
       </c>
-      <c r="R20" s="3"/>
-    </row>
-    <row r="21" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S20" s="3"/>
+    </row>
+    <row r="21" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>25239000</v>
+      </c>
+      <c r="E21" s="3">
         <v>24571000</v>
       </c>
-      <c r="E21" s="3">
-        <v>24115000</v>
-      </c>
       <c r="F21" s="3">
+        <v>23457000</v>
+      </c>
+      <c r="G21" s="3">
         <v>21525000</v>
       </c>
-      <c r="G21" s="3">
+      <c r="H21" s="3">
         <v>21195000</v>
       </c>
-      <c r="H21" s="3">
+      <c r="I21" s="3">
         <v>20826000</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>19170000</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>17548000</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>16258000</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>16542000</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>17026000</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>14772000</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>17359000</v>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>18495000</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="R21" s="3">
         <v>16758000</v>
       </c>
-      <c r="R21" s="3"/>
-    </row>
-    <row r="22" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S21" s="3"/>
+    </row>
+    <row r="22" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
       <c r="D22" s="3">
+        <v>877000</v>
+      </c>
+      <c r="E22" s="3">
         <v>907000</v>
       </c>
-      <c r="E22" s="3">
+      <c r="F22" s="3">
         <v>925000</v>
       </c>
-      <c r="F22" s="3">
+      <c r="G22" s="3">
         <v>756000</v>
       </c>
-      <c r="G22" s="3">
+      <c r="H22" s="3">
         <v>439000</v>
       </c>
-      <c r="H22" s="3">
+      <c r="I22" s="3">
         <v>502000</v>
       </c>
-      <c r="I22" s="3">
+      <c r="J22" s="3">
         <v>465000</v>
       </c>
-      <c r="J22" s="3">
+      <c r="K22" s="3">
         <v>509000</v>
       </c>
-      <c r="K22" s="3">
+      <c r="L22" s="3">
         <v>506000</v>
       </c>
-      <c r="L22" s="3">
+      <c r="M22" s="3">
         <v>465000</v>
       </c>
-      <c r="M22" s="3">
+      <c r="N22" s="3">
         <v>579000</v>
       </c>
-      <c r="N22" s="3">
+      <c r="O22" s="3">
         <v>626000</v>
       </c>
-      <c r="O22" s="3">
+      <c r="P22" s="3">
         <v>709000</v>
       </c>
-      <c r="P22" s="3">
+      <c r="Q22" s="3">
         <v>1334000</v>
       </c>
-      <c r="Q22" s="3">
+      <c r="R22" s="3">
         <v>769000</v>
       </c>
-      <c r="R22" s="3"/>
-    </row>
-    <row r="23" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S22" s="3"/>
+    </row>
+    <row r="23" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>20377000</v>
+      </c>
+      <c r="E23" s="3">
         <v>20167000</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>18761000</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>18353000</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>17995000</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>17615000</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>15834000</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>6069000</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>13326000</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>13257000</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>13369000</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>11012000</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>13509000</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>14179000</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>12785000</v>
       </c>
-      <c r="R23" s="3"/>
-    </row>
-    <row r="24" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S23" s="3"/>
+    </row>
+    <row r="24" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
+        <v>4233000</v>
+      </c>
+      <c r="E24" s="3">
         <v>4102000</v>
       </c>
-      <c r="E24" s="3">
+      <c r="F24" s="3">
         <v>3787000</v>
       </c>
-      <c r="F24" s="3">
+      <c r="G24" s="3">
         <v>3615000</v>
       </c>
-      <c r="G24" s="3">
+      <c r="H24" s="3">
         <v>3202000</v>
       </c>
-      <c r="H24" s="3">
+      <c r="I24" s="3">
         <v>3263000</v>
       </c>
-      <c r="I24" s="3">
+      <c r="J24" s="3">
         <v>2731000</v>
       </c>
-      <c r="J24" s="3">
+      <c r="K24" s="3">
         <v>2103000</v>
       </c>
-      <c r="K24" s="3">
+      <c r="L24" s="3">
         <v>3465000</v>
       </c>
-      <c r="L24" s="3">
+      <c r="M24" s="3">
         <v>3063000</v>
       </c>
-      <c r="M24" s="3">
+      <c r="N24" s="3">
         <v>3342000</v>
       </c>
-      <c r="N24" s="3">
+      <c r="O24" s="3">
         <v>2725000</v>
       </c>
-      <c r="O24" s="3">
+      <c r="P24" s="3">
         <v>2851000</v>
       </c>
-      <c r="P24" s="3">
+      <c r="Q24" s="3">
         <v>3226000</v>
       </c>
-      <c r="Q24" s="3">
+      <c r="R24" s="3">
         <v>3468000</v>
       </c>
-      <c r="R24" s="3"/>
-    </row>
-    <row r="25" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S24" s="3"/>
+    </row>
+    <row r="25" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -1499,105 +1547,114 @@
       <c r="Q25" s="3">
         <v>0</v>
       </c>
-      <c r="R25" s="3"/>
-    </row>
-    <row r="26" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R25" s="3">
+        <v>0</v>
+      </c>
+      <c r="S25" s="3"/>
+    </row>
+    <row r="26" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>16144000</v>
+      </c>
+      <c r="E26" s="3">
         <v>16065000</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>14974000</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>14738000</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>14793000</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>14352000</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>13103000</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>3966000</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>9861000</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>10194000</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>10027000</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>8287000</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>10658000</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>10953000</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>9317000</v>
       </c>
-      <c r="R26" s="3"/>
-    </row>
-    <row r="27" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S26" s="3"/>
+    </row>
+    <row r="27" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>15754000</v>
+      </c>
+      <c r="E27" s="3">
         <v>15683000</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>14595000</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>14371000</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>14461000</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>14035000</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>12764000</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>3634000</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>9485000</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>9862000</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>9676000</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>7920000</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>10263000</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>10619000</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>8913000</v>
       </c>
-      <c r="R27" s="3"/>
-    </row>
-    <row r="28" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S27" s="3"/>
+    </row>
+    <row r="28" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -1643,9 +1700,12 @@
       <c r="Q28" s="3">
         <v>0</v>
       </c>
-      <c r="R28" s="3"/>
-    </row>
-    <row r="29" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R28" s="3">
+        <v>0</v>
+      </c>
+      <c r="S28" s="3"/>
+    </row>
+    <row r="29" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -1674,26 +1734,29 @@
         <v>0</v>
       </c>
       <c r="L29" s="3">
+        <v>0</v>
+      </c>
+      <c r="M29" s="3">
         <v>5217000</v>
       </c>
-      <c r="M29" s="3">
+      <c r="N29" s="3">
         <v>577000</v>
       </c>
-      <c r="N29" s="3">
+      <c r="O29" s="3">
         <v>-1143000</v>
       </c>
-      <c r="O29" s="3">
+      <c r="P29" s="3">
         <v>1127000</v>
       </c>
-      <c r="P29" s="3">
+      <c r="Q29" s="3">
         <v>449000</v>
       </c>
-      <c r="Q29" s="3">
+      <c r="R29" s="3">
         <v>3174000</v>
       </c>
-      <c r="R29" s="3"/>
-    </row>
-    <row r="30" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S29" s="3"/>
+    </row>
+    <row r="30" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -1739,9 +1802,12 @@
       <c r="Q30" s="3">
         <v>0</v>
       </c>
-      <c r="R30" s="3"/>
-    </row>
-    <row r="31" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R30" s="3">
+        <v>0</v>
+      </c>
+      <c r="S30" s="3"/>
+    </row>
+    <row r="31" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -1787,105 +1853,114 @@
       <c r="Q31" s="3">
         <v>0</v>
       </c>
-      <c r="R31" s="3"/>
-    </row>
-    <row r="32" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R31" s="3">
+        <v>0</v>
+      </c>
+      <c r="S31" s="3"/>
+    </row>
+    <row r="32" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
+        <v>487000</v>
+      </c>
+      <c r="E32" s="3">
         <v>116000</v>
       </c>
-      <c r="E32" s="3">
-        <v>271000</v>
-      </c>
       <c r="F32" s="3">
+        <v>16000</v>
+      </c>
+      <c r="G32" s="3">
         <v>74000</v>
       </c>
-      <c r="G32" s="3">
+      <c r="H32" s="3">
         <v>-57000</v>
       </c>
-      <c r="H32" s="3">
+      <c r="I32" s="3">
         <v>-392000</v>
       </c>
-      <c r="I32" s="3">
+      <c r="J32" s="3">
         <v>54000</v>
       </c>
-      <c r="J32" s="3">
+      <c r="K32" s="3">
         <v>517000</v>
       </c>
-      <c r="K32" s="3">
+      <c r="L32" s="3">
         <v>-265000</v>
       </c>
-      <c r="L32" s="3">
+      <c r="M32" s="3">
         <v>233000</v>
       </c>
-      <c r="M32" s="3">
+      <c r="N32" s="3">
         <v>-507000</v>
       </c>
-      <c r="N32" s="3">
+      <c r="O32" s="3">
         <v>-589000</v>
       </c>
-      <c r="O32" s="3">
+      <c r="P32" s="3">
         <v>-308000</v>
       </c>
-      <c r="P32" s="3">
+      <c r="Q32" s="3">
         <v>-1696000</v>
       </c>
-      <c r="Q32" s="3">
+      <c r="R32" s="3">
         <v>-262000</v>
       </c>
-      <c r="R32" s="3"/>
-    </row>
-    <row r="33" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S32" s="3"/>
+    </row>
+    <row r="33" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>16046000</v>
+      </c>
+      <c r="E33" s="3">
         <v>15974000</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>14879000</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>14653000</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>14742000</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>14306000</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>13027000</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>3897000</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>9750000</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>15079000</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>10253000</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>6777000</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>11390000</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>11068000</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>12087000</v>
       </c>
-      <c r="R33" s="3"/>
-    </row>
-    <row r="34" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S33" s="3"/>
+    </row>
+    <row r="34" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -1931,110 +2006,119 @@
       <c r="Q34" s="3">
         <v>0</v>
       </c>
-      <c r="R34" s="3"/>
-    </row>
-    <row r="35" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="R34" s="3">
+        <v>0</v>
+      </c>
+      <c r="S34" s="3"/>
+    </row>
+    <row r="35" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>16046000</v>
+      </c>
+      <c r="E35" s="3">
         <v>15974000</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>14879000</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>14653000</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>14742000</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>14306000</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>13027000</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>3897000</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>9750000</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>15079000</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>10253000</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>6777000</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>11390000</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>11068000</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>12087000</v>
       </c>
-      <c r="R35" s="3"/>
-    </row>
-    <row r="37" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S35" s="3"/>
+    </row>
+    <row r="37" spans="2:19" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:18" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>46203</v>
+      </c>
+      <c r="E38" s="2">
         <v>45838</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45473</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45107</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>44742</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>44377</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>44012</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>43646</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>43281</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>42916</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>42551</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>42185</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>41820</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>41455</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>41090</v>
       </c>
-      <c r="R38" s="2"/>
-    </row>
-    <row r="39" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S38" s="2"/>
+    </row>
+    <row r="39" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -2053,8 +2137,9 @@
       <c r="P39" s="3"/>
       <c r="Q39" s="3"/>
       <c r="R39" s="3"/>
-    </row>
-    <row r="40" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S39" s="3"/>
+    </row>
+    <row r="40" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -2073,56 +2158,60 @@
       <c r="P40" s="3"/>
       <c r="Q40" s="3"/>
       <c r="R40" s="3"/>
-    </row>
-    <row r="41" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S40" s="3"/>
+    </row>
+    <row r="41" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>9942000</v>
+      </c>
+      <c r="E41" s="3">
         <v>9556000</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>9482000</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>8246000</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>7214000</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>10288000</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>16181000</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>4239000</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>2569000</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>5569000</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>7102000</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>6836000</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>8558000</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>5947000</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>4436000</v>
       </c>
-      <c r="R41" s="3"/>
-    </row>
-    <row r="42" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S41" s="3"/>
+    </row>
+    <row r="42" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
@@ -2145,136 +2234,145 @@
         <v>0</v>
       </c>
       <c r="J42" s="3">
+        <v>0</v>
+      </c>
+      <c r="K42" s="3">
         <v>6048000</v>
       </c>
-      <c r="K42" s="3">
+      <c r="L42" s="3">
         <v>9281000</v>
       </c>
-      <c r="L42" s="3">
+      <c r="M42" s="3">
         <v>9568000</v>
       </c>
-      <c r="M42" s="3">
+      <c r="N42" s="3">
         <v>6246000</v>
       </c>
-      <c r="N42" s="3">
+      <c r="O42" s="3">
         <v>4767000</v>
       </c>
-      <c r="O42" s="3">
+      <c r="P42" s="3">
         <v>2128000</v>
-      </c>
-      <c r="P42" s="3" t="s">
-        <v>8</v>
       </c>
       <c r="Q42" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="R42" s="3"/>
-    </row>
-    <row r="43" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="R42" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="S42" s="3"/>
+    </row>
+    <row r="43" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>6056000</v>
+      </c>
+      <c r="E43" s="3">
         <v>6185000</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>6118000</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>5471000</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>5143000</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>4725000</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>4178000</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>4951000</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>4686000</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>4594000</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>4373000</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>4568000</v>
       </c>
-      <c r="O43" s="3">
+      <c r="P43" s="3">
         <v>6386000</v>
       </c>
-      <c r="P43" s="3">
+      <c r="Q43" s="3">
         <v>6508000</v>
       </c>
-      <c r="Q43" s="3">
+      <c r="R43" s="3">
         <v>6068000</v>
       </c>
-      <c r="R43" s="3"/>
-    </row>
-    <row r="44" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S43" s="3"/>
+    </row>
+    <row r="44" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D44" s="3">
+        <v>8170000</v>
+      </c>
+      <c r="E44" s="3">
         <v>7550000</v>
       </c>
-      <c r="E44" s="3">
+      <c r="F44" s="3">
         <v>7016000</v>
       </c>
-      <c r="F44" s="3">
+      <c r="G44" s="3">
         <v>7073000</v>
       </c>
-      <c r="G44" s="3">
+      <c r="H44" s="3">
         <v>6924000</v>
       </c>
-      <c r="H44" s="3">
+      <c r="I44" s="3">
         <v>5983000</v>
       </c>
-      <c r="I44" s="3">
+      <c r="J44" s="3">
         <v>5498000</v>
       </c>
-      <c r="J44" s="3">
+      <c r="K44" s="3">
         <v>5017000</v>
       </c>
-      <c r="K44" s="3">
+      <c r="L44" s="3">
         <v>4738000</v>
       </c>
-      <c r="L44" s="3">
+      <c r="M44" s="3">
         <v>4624000</v>
       </c>
-      <c r="M44" s="3">
+      <c r="N44" s="3">
         <v>4716000</v>
       </c>
-      <c r="N44" s="3">
+      <c r="O44" s="3">
         <v>4979000</v>
       </c>
-      <c r="O44" s="3">
+      <c r="P44" s="3">
         <v>6759000</v>
       </c>
-      <c r="P44" s="3">
+      <c r="Q44" s="3">
         <v>6909000</v>
       </c>
-      <c r="Q44" s="3">
+      <c r="R44" s="3">
         <v>6721000</v>
       </c>
-      <c r="R44" s="3"/>
-    </row>
-    <row r="45" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S44" s="3"/>
+    </row>
+    <row r="45" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
-      <c r="D45" s="3">
+      <c r="D45" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E45" s="3">
         <v>1000</v>
-      </c>
-      <c r="E45" s="3" t="s">
-        <v>8</v>
       </c>
       <c r="F45" s="3" t="s">
         <v>8</v>
@@ -2294,75 +2392,81 @@
       <c r="K45" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="L45" s="3">
+      <c r="L45" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="M45" s="3">
         <v>2139000</v>
       </c>
-      <c r="M45" s="3">
+      <c r="N45" s="3">
         <v>11345000</v>
       </c>
-      <c r="N45" s="3">
+      <c r="O45" s="3">
         <v>8496000</v>
       </c>
-      <c r="O45" s="3">
+      <c r="P45" s="3">
         <v>7786000</v>
       </c>
-      <c r="P45" s="3">
+      <c r="Q45" s="3">
         <v>4626000</v>
       </c>
-      <c r="Q45" s="3">
+      <c r="R45" s="3">
         <v>4685000</v>
       </c>
-      <c r="R45" s="3"/>
-    </row>
-    <row r="46" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S45" s="3"/>
+    </row>
+    <row r="46" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>26208000</v>
+      </c>
+      <c r="E46" s="3">
         <v>25392000</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>24709000</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>22648000</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>21653000</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>23091000</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>27987000</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>22473000</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>23320000</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>26494000</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>33782000</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>29646000</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>31617000</v>
       </c>
-      <c r="P46" s="3">
+      <c r="Q46" s="3">
         <v>23990000</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="R46" s="3">
         <v>21910000</v>
       </c>
-      <c r="R46" s="3"/>
-    </row>
-    <row r="47" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S46" s="3"/>
+    </row>
+    <row r="47" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
@@ -2378,26 +2482,26 @@
       <c r="G47" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="H47" s="3">
+      <c r="H47" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="I47" s="3">
         <v>192000</v>
       </c>
-      <c r="I47" s="3">
+      <c r="J47" s="3">
         <v>67000</v>
       </c>
-      <c r="J47" s="3">
+      <c r="K47" s="3">
         <v>169000</v>
       </c>
-      <c r="K47" s="3">
+      <c r="L47" s="3">
         <v>141000</v>
-      </c>
-      <c r="L47" s="3" t="s">
-        <v>8</v>
       </c>
       <c r="M47" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="N47" s="3">
-        <v>0</v>
+      <c r="N47" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="O47" s="3">
         <v>0</v>
@@ -2408,105 +2512,114 @@
       <c r="Q47" s="3">
         <v>0</v>
       </c>
-      <c r="R47" s="3"/>
-    </row>
-    <row r="48" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="R47" s="3">
+        <v>0</v>
+      </c>
+      <c r="S47" s="3"/>
+    </row>
+    <row r="48" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>26206000</v>
+      </c>
+      <c r="E48" s="3">
         <v>24822000</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>23027000</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>22690000</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>21955000</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>22494000</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>21542000</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>21271000</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>20600000</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>19893000</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>19385000</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>39310000</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>22304000</v>
       </c>
-      <c r="P48" s="3">
+      <c r="Q48" s="3">
         <v>21666000</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="R48" s="3">
         <v>20377000</v>
       </c>
-      <c r="R48" s="3"/>
-    </row>
-    <row r="49" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S48" s="3"/>
+    </row>
+    <row r="49" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>62720000</v>
+      </c>
+      <c r="E49" s="3">
         <v>63560000</v>
       </c>
-      <c r="E49" s="3">
+      <c r="F49" s="3">
         <v>62350000</v>
       </c>
-      <c r="F49" s="3">
+      <c r="G49" s="3">
         <v>64442000</v>
       </c>
-      <c r="G49" s="3">
+      <c r="H49" s="3">
         <v>63379000</v>
       </c>
-      <c r="H49" s="3">
+      <c r="I49" s="3">
         <v>64566000</v>
       </c>
-      <c r="I49" s="3">
+      <c r="J49" s="3">
         <v>63693000</v>
       </c>
-      <c r="J49" s="3">
+      <c r="K49" s="3">
         <v>64488000</v>
       </c>
-      <c r="K49" s="3">
+      <c r="L49" s="3">
         <v>69077000</v>
       </c>
-      <c r="L49" s="3">
+      <c r="M49" s="3">
         <v>68886000</v>
       </c>
-      <c r="M49" s="3">
+      <c r="N49" s="3">
         <v>68877000</v>
       </c>
-      <c r="N49" s="3">
+      <c r="O49" s="3">
         <v>94642000</v>
       </c>
-      <c r="O49" s="3">
+      <c r="P49" s="3">
         <v>84547000</v>
       </c>
-      <c r="P49" s="3">
+      <c r="Q49" s="3">
         <v>86760000</v>
       </c>
-      <c r="Q49" s="3">
+      <c r="R49" s="3">
         <v>84761000</v>
       </c>
-      <c r="R49" s="3"/>
-    </row>
-    <row r="50" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S49" s="3"/>
+    </row>
+    <row r="50" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -2552,9 +2665,12 @@
       <c r="Q50" s="3">
         <v>0</v>
       </c>
-      <c r="R50" s="3"/>
-    </row>
-    <row r="51" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R50" s="3">
+        <v>0</v>
+      </c>
+      <c r="S50" s="3"/>
+    </row>
+    <row r="51" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -2600,57 +2716,63 @@
       <c r="Q51" s="3">
         <v>0</v>
       </c>
-      <c r="R51" s="3"/>
-    </row>
-    <row r="52" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R51" s="3">
+        <v>0</v>
+      </c>
+      <c r="S51" s="3"/>
+    </row>
+    <row r="52" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>11387000</v>
+      </c>
+      <c r="E52" s="3">
         <v>11457000</v>
       </c>
-      <c r="E52" s="3">
+      <c r="F52" s="3">
         <v>12284000</v>
       </c>
-      <c r="F52" s="3">
+      <c r="G52" s="3">
         <v>11049000</v>
       </c>
-      <c r="G52" s="3">
+      <c r="H52" s="3">
         <v>10221000</v>
       </c>
-      <c r="H52" s="3">
+      <c r="I52" s="3">
         <v>8964000</v>
       </c>
-      <c r="I52" s="3">
+      <c r="J52" s="3">
         <v>7411000</v>
       </c>
-      <c r="J52" s="3">
+      <c r="K52" s="3">
         <v>6694000</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>5172000</v>
       </c>
-      <c r="L52" s="3">
+      <c r="M52" s="3">
         <v>5133000</v>
       </c>
-      <c r="M52" s="3">
+      <c r="N52" s="3">
         <v>5092000</v>
       </c>
-      <c r="N52" s="3">
+      <c r="O52" s="3">
         <v>10562000</v>
       </c>
-      <c r="O52" s="3">
+      <c r="P52" s="3">
         <v>5798000</v>
       </c>
-      <c r="P52" s="3">
+      <c r="Q52" s="3">
         <v>6847000</v>
       </c>
-      <c r="Q52" s="3">
+      <c r="R52" s="3">
         <v>5196000</v>
       </c>
-      <c r="R52" s="3"/>
-    </row>
-    <row r="53" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S52" s="3"/>
+    </row>
+    <row r="53" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -2696,57 +2818,63 @@
       <c r="Q53" s="3">
         <v>0</v>
       </c>
-      <c r="R53" s="3"/>
-    </row>
-    <row r="54" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R53" s="3">
+        <v>0</v>
+      </c>
+      <c r="S53" s="3"/>
+    </row>
+    <row r="54" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>126521000</v>
+      </c>
+      <c r="E54" s="3">
         <v>125231000</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>122370000</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>120829000</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>117208000</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>119307000</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>120700000</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>115095000</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>118310000</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>120406000</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>127136000</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>129495000</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>144266000</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>139263000</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>132244000</v>
       </c>
-      <c r="R54" s="3"/>
-    </row>
-    <row r="55" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S54" s="3"/>
+    </row>
+    <row r="55" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -2765,8 +2893,9 @@
       <c r="P55" s="3"/>
       <c r="Q55" s="3"/>
       <c r="R55" s="3"/>
-    </row>
-    <row r="56" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S55" s="3"/>
+    </row>
+    <row r="56" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -2785,296 +2914,315 @@
       <c r="P56" s="3"/>
       <c r="Q56" s="3"/>
       <c r="R56" s="3"/>
-    </row>
-    <row r="57" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S56" s="3"/>
+    </row>
+    <row r="57" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>16306000</v>
+      </c>
+      <c r="E57" s="3">
         <v>15227000</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>15364000</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>14598000</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>14882000</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>13720000</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>12071000</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>11260000</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>10344000</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>9632000</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>9325000</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>8138000</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>8461000</v>
       </c>
-      <c r="P57" s="3">
+      <c r="Q57" s="3">
         <v>8777000</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="R57" s="3">
         <v>7920000</v>
       </c>
-      <c r="R57" s="3"/>
-    </row>
-    <row r="58" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S57" s="3"/>
+    </row>
+    <row r="58" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>11542000</v>
+      </c>
+      <c r="E58" s="3">
         <v>10395000</v>
       </c>
-      <c r="E58" s="3">
+      <c r="F58" s="3">
         <v>7465000</v>
       </c>
-      <c r="F58" s="3">
+      <c r="G58" s="3">
         <v>11082000</v>
       </c>
-      <c r="G58" s="3">
+      <c r="H58" s="3">
         <v>8850000</v>
       </c>
-      <c r="H58" s="3">
+      <c r="I58" s="3">
         <v>9108000</v>
       </c>
-      <c r="I58" s="3">
+      <c r="J58" s="3">
         <v>11422000</v>
       </c>
-      <c r="J58" s="3">
+      <c r="K58" s="3">
         <v>9697000</v>
       </c>
-      <c r="K58" s="3">
+      <c r="L58" s="3">
         <v>10423000</v>
       </c>
-      <c r="L58" s="3">
+      <c r="M58" s="3">
         <v>13554000</v>
       </c>
-      <c r="M58" s="3">
+      <c r="N58" s="3">
         <v>11653000</v>
       </c>
-      <c r="N58" s="3">
+      <c r="O58" s="3">
         <v>26808000</v>
       </c>
-      <c r="O58" s="3">
+      <c r="P58" s="3">
         <v>15606000</v>
       </c>
-      <c r="P58" s="3">
+      <c r="Q58" s="3">
         <v>12432000</v>
       </c>
-      <c r="Q58" s="3">
+      <c r="R58" s="3">
         <v>8698000</v>
       </c>
-      <c r="R58" s="3"/>
-    </row>
-    <row r="59" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S58" s="3"/>
+    </row>
+    <row r="59" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>4361000</v>
+      </c>
+      <c r="E59" s="3">
         <v>4286000</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>4183000</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>3917000</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>3674000</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>4019000</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>4031000</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>3132000</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>2964000</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>7024000</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>9792000</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>17725000</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>9659000</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>8828000</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="R59" s="3">
         <v>8289000</v>
       </c>
-      <c r="R59" s="3"/>
-    </row>
-    <row r="60" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S59" s="3"/>
+    </row>
+    <row r="60" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>38694000</v>
+      </c>
+      <c r="E60" s="3">
         <v>36058000</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>33627000</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>35756000</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>33081000</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>33132000</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>32976000</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>30011000</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>28237000</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>30210000</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>30770000</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>29790000</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>33726000</v>
       </c>
-      <c r="P60" s="3">
+      <c r="Q60" s="3">
         <v>30037000</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="R60" s="3">
         <v>24907000</v>
       </c>
-      <c r="R60" s="3"/>
-    </row>
-    <row r="61" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S60" s="3"/>
+    </row>
+    <row r="61" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>23483000</v>
+      </c>
+      <c r="E61" s="3">
         <v>26131000</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>26260000</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>25418000</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>23443000</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>23730000</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>24189000</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>20395000</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>20863000</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>18038000</v>
       </c>
-      <c r="M61" s="3">
+      <c r="N61" s="3">
         <v>18945000</v>
       </c>
-      <c r="N61" s="3">
+      <c r="O61" s="3">
         <v>18327000</v>
       </c>
-      <c r="O61" s="3">
+      <c r="P61" s="3">
         <v>19811000</v>
       </c>
-      <c r="P61" s="3">
+      <c r="Q61" s="3">
         <v>19111000</v>
       </c>
-      <c r="Q61" s="3">
+      <c r="R61" s="3">
         <v>21080000</v>
       </c>
-      <c r="R61" s="3"/>
-    </row>
-    <row r="62" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S61" s="3"/>
+    </row>
+    <row r="62" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>1333000</v>
+      </c>
+      <c r="E62" s="3">
         <v>1267000</v>
       </c>
-      <c r="E62" s="3">
+      <c r="F62" s="3">
         <v>1872000</v>
       </c>
-      <c r="F62" s="3">
+      <c r="G62" s="3">
         <v>2306000</v>
       </c>
-      <c r="G62" s="3">
+      <c r="H62" s="3">
         <v>3210000</v>
       </c>
-      <c r="H62" s="3">
+      <c r="I62" s="3">
         <v>3264000</v>
       </c>
-      <c r="I62" s="3">
+      <c r="J62" s="3">
         <v>3270000</v>
       </c>
-      <c r="J62" s="3">
+      <c r="K62" s="3">
         <v>3491000</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>3901000</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>16380000</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>19438000</v>
       </c>
-      <c r="N62" s="3">
+      <c r="O62" s="3">
         <v>26043000</v>
       </c>
-      <c r="O62" s="3">
+      <c r="P62" s="3">
         <v>20753000</v>
       </c>
-      <c r="P62" s="3">
+      <c r="Q62" s="3">
         <v>21406000</v>
       </c>
-      <c r="Q62" s="3">
+      <c r="R62" s="3">
         <v>22222000</v>
       </c>
-      <c r="R62" s="3"/>
-    </row>
-    <row r="63" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S62" s="3"/>
+    </row>
+    <row r="63" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -3120,9 +3268,12 @@
       <c r="Q63" s="3">
         <v>0</v>
       </c>
-      <c r="R63" s="3"/>
-    </row>
-    <row r="64" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R63" s="3">
+        <v>0</v>
+      </c>
+      <c r="S63" s="3"/>
+    </row>
+    <row r="64" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -3168,9 +3319,12 @@
       <c r="Q64" s="3">
         <v>0</v>
       </c>
-      <c r="R64" s="3"/>
-    </row>
-    <row r="65" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="R64" s="3">
+        <v>0</v>
+      </c>
+      <c r="S64" s="3"/>
+    </row>
+    <row r="65" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -3216,57 +3370,63 @@
       <c r="Q65" s="3">
         <v>0</v>
       </c>
-      <c r="R65" s="3"/>
-    </row>
-    <row r="66" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="R65" s="3">
+        <v>0</v>
+      </c>
+      <c r="S65" s="3"/>
+    </row>
+    <row r="66" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>72210000</v>
+      </c>
+      <c r="E66" s="3">
         <v>72947000</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>71812000</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>73764000</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>70354000</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>72653000</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>73822000</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>67516000</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>65427000</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>65222000</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>69795000</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>67076000</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>75052000</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>71199000</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>68805000</v>
       </c>
-      <c r="R66" s="3"/>
-    </row>
-    <row r="67" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S66" s="3"/>
+    </row>
+    <row r="67" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -3285,8 +3445,9 @@
       <c r="P67" s="3"/>
       <c r="Q67" s="3"/>
       <c r="R67" s="3"/>
-    </row>
-    <row r="68" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S67" s="3"/>
+    </row>
+    <row r="68" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -3332,9 +3493,12 @@
       <c r="Q68" s="3">
         <v>0</v>
       </c>
-      <c r="R68" s="3"/>
-    </row>
-    <row r="69" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="R68" s="3">
+        <v>0</v>
+      </c>
+      <c r="S68" s="3"/>
+    </row>
+    <row r="69" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -3380,57 +3544,63 @@
       <c r="Q69" s="3">
         <v>0</v>
       </c>
-      <c r="R69" s="3"/>
-    </row>
-    <row r="70" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="R69" s="3">
+        <v>0</v>
+      </c>
+      <c r="S69" s="3"/>
+    </row>
+    <row r="70" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
       <c r="D70" s="3">
+        <v>756000</v>
+      </c>
+      <c r="E70" s="3">
         <v>777000</v>
       </c>
-      <c r="E70" s="3">
+      <c r="F70" s="3">
         <v>798000</v>
       </c>
-      <c r="F70" s="3">
+      <c r="G70" s="3">
         <v>819000</v>
       </c>
-      <c r="G70" s="3">
+      <c r="H70" s="3">
         <v>843000</v>
       </c>
-      <c r="H70" s="3">
+      <c r="I70" s="3">
         <v>870000</v>
       </c>
-      <c r="I70" s="3">
+      <c r="J70" s="3">
         <v>897000</v>
       </c>
-      <c r="J70" s="3">
+      <c r="K70" s="3">
         <v>928000</v>
       </c>
-      <c r="K70" s="3">
+      <c r="L70" s="3">
         <v>967000</v>
       </c>
-      <c r="L70" s="3">
+      <c r="M70" s="3">
         <v>1006000</v>
       </c>
-      <c r="M70" s="3">
+      <c r="N70" s="3">
         <v>1038000</v>
       </c>
-      <c r="N70" s="3">
+      <c r="O70" s="3">
         <v>1077000</v>
       </c>
-      <c r="O70" s="3">
+      <c r="P70" s="3">
         <v>1111000</v>
       </c>
-      <c r="P70" s="3">
+      <c r="Q70" s="3">
         <v>1137000</v>
       </c>
-      <c r="Q70" s="3">
+      <c r="R70" s="3">
         <v>1195000</v>
       </c>
-      <c r="R70" s="3"/>
-    </row>
-    <row r="71" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S70" s="3"/>
+    </row>
+    <row r="71" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -3476,57 +3646,63 @@
       <c r="Q71" s="3">
         <v>0</v>
       </c>
-      <c r="R71" s="3"/>
-    </row>
-    <row r="72" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="R71" s="3">
+        <v>0</v>
+      </c>
+      <c r="S71" s="3"/>
+    </row>
+    <row r="72" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>135852000</v>
+      </c>
+      <c r="E72" s="3">
         <v>129973000</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>123811000</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>118170000</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>112429000</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>106374000</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>100239000</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>94918000</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>98641000</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>96124000</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>87953000</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>84807000</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>84990000</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>80197000</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>75349000</v>
       </c>
-      <c r="R72" s="3"/>
-    </row>
-    <row r="73" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S72" s="3"/>
+    </row>
+    <row r="73" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -3572,9 +3748,12 @@
       <c r="Q73" s="3">
         <v>0</v>
       </c>
-      <c r="R73" s="3"/>
-    </row>
-    <row r="74" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="R73" s="3">
+        <v>0</v>
+      </c>
+      <c r="S73" s="3"/>
+    </row>
+    <row r="74" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -3620,9 +3799,12 @@
       <c r="Q74" s="3">
         <v>0</v>
       </c>
-      <c r="R74" s="3"/>
-    </row>
-    <row r="75" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="R74" s="3">
+        <v>0</v>
+      </c>
+      <c r="S74" s="3"/>
+    </row>
+    <row r="75" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -3668,57 +3850,63 @@
       <c r="Q75" s="3">
         <v>0</v>
       </c>
-      <c r="R75" s="3"/>
-    </row>
-    <row r="76" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="R75" s="3">
+        <v>0</v>
+      </c>
+      <c r="S75" s="3"/>
+    </row>
+    <row r="76" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>53325000</v>
+      </c>
+      <c r="E76" s="3">
         <v>51235000</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>49488000</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>45958000</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>45746000</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>45508000</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>45624000</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>46266000</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>51326000</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>54178000</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>56303000</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>61342000</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>68103000</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>66927000</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>62244000</v>
       </c>
-      <c r="R76" s="3"/>
-    </row>
-    <row r="77" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S76" s="3"/>
+    </row>
+    <row r="77" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -3764,110 +3952,119 @@
       <c r="Q77" s="3">
         <v>0</v>
       </c>
-      <c r="R77" s="3"/>
-    </row>
-    <row r="79" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="R77" s="3">
+        <v>0</v>
+      </c>
+      <c r="S77" s="3"/>
+    </row>
+    <row r="79" spans="2:19" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:18" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>46203</v>
+      </c>
+      <c r="E80" s="2">
         <v>45838</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45473</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45107</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>44742</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>44377</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>44012</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>43646</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>43281</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>42916</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>42551</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>42185</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>41820</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>41455</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>41090</v>
       </c>
-      <c r="R80" s="2"/>
-    </row>
-    <row r="81" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S80" s="2"/>
+    </row>
+    <row r="81" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>16046000</v>
+      </c>
+      <c r="E81" s="3">
         <v>15974000</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>14879000</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>14653000</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>14742000</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>14306000</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>13027000</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>3897000</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>9750000</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>15079000</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>10253000</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>6777000</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>11390000</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>11068000</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>12087000</v>
       </c>
-      <c r="R81" s="3"/>
-    </row>
-    <row r="82" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S81" s="3"/>
+    </row>
+    <row r="82" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -3886,56 +4083,60 @@
       <c r="P82" s="3"/>
       <c r="Q82" s="3"/>
       <c r="R82" s="3"/>
-    </row>
-    <row r="83" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S82" s="3"/>
+    </row>
+    <row r="83" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
+        <v>2852000</v>
+      </c>
+      <c r="E83" s="3">
         <v>2527000</v>
       </c>
-      <c r="E83" s="3">
+      <c r="F83" s="3">
         <v>2558000</v>
       </c>
-      <c r="F83" s="3">
+      <c r="G83" s="3">
         <v>2387000</v>
       </c>
-      <c r="G83" s="3">
+      <c r="H83" s="3">
         <v>2495000</v>
       </c>
-      <c r="H83" s="3">
+      <c r="I83" s="3">
         <v>2417000</v>
       </c>
-      <c r="I83" s="3">
+      <c r="J83" s="3">
         <v>2653000</v>
       </c>
-      <c r="J83" s="3">
+      <c r="K83" s="3">
         <v>2475000</v>
       </c>
-      <c r="K83" s="3">
+      <c r="L83" s="3">
         <v>2532000</v>
       </c>
-      <c r="L83" s="3">
+      <c r="M83" s="3">
         <v>2820000</v>
       </c>
-      <c r="M83" s="3">
+      <c r="N83" s="3">
         <v>3078000</v>
       </c>
-      <c r="N83" s="3">
+      <c r="O83" s="3">
         <v>3134000</v>
       </c>
-      <c r="O83" s="3">
+      <c r="P83" s="3">
         <v>3141000</v>
       </c>
-      <c r="P83" s="3">
+      <c r="Q83" s="3">
         <v>2982000</v>
       </c>
-      <c r="Q83" s="3">
+      <c r="R83" s="3">
         <v>3204000</v>
       </c>
-      <c r="R83" s="3"/>
-    </row>
-    <row r="84" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S83" s="3"/>
+    </row>
+    <row r="84" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -3981,9 +4182,12 @@
       <c r="Q84" s="3">
         <v>0</v>
       </c>
-      <c r="R84" s="3"/>
-    </row>
-    <row r="85" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R84" s="3">
+        <v>0</v>
+      </c>
+      <c r="S84" s="3"/>
+    </row>
+    <row r="85" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -4029,9 +4233,12 @@
       <c r="Q85" s="3">
         <v>0</v>
       </c>
-      <c r="R85" s="3"/>
-    </row>
-    <row r="86" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R85" s="3">
+        <v>0</v>
+      </c>
+      <c r="S85" s="3"/>
+    </row>
+    <row r="86" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -4077,9 +4284,12 @@
       <c r="Q86" s="3">
         <v>0</v>
       </c>
-      <c r="R86" s="3"/>
-    </row>
-    <row r="87" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R86" s="3">
+        <v>0</v>
+      </c>
+      <c r="S86" s="3"/>
+    </row>
+    <row r="87" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -4125,9 +4335,12 @@
       <c r="Q87" s="3">
         <v>0</v>
       </c>
-      <c r="R87" s="3"/>
-    </row>
-    <row r="88" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R87" s="3">
+        <v>0</v>
+      </c>
+      <c r="S87" s="3"/>
+    </row>
+    <row r="88" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -4173,57 +4386,63 @@
       <c r="Q88" s="3">
         <v>0</v>
       </c>
-      <c r="R88" s="3"/>
-    </row>
-    <row r="89" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R88" s="3">
+        <v>0</v>
+      </c>
+      <c r="S88" s="3"/>
+    </row>
+    <row r="89" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>19556000</v>
+      </c>
+      <c r="E89" s="3">
         <v>17817000</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>19846000</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>16848000</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>16723000</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>18371000</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>17403000</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>15242000</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>14867000</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>12753000</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>15435000</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>14608000</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>13958000</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>14873000</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>13284000</v>
       </c>
-      <c r="R89" s="3"/>
-    </row>
-    <row r="90" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S89" s="3"/>
+    </row>
+    <row r="90" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -4242,56 +4461,60 @@
       <c r="P90" s="3"/>
       <c r="Q90" s="3"/>
       <c r="R90" s="3"/>
-    </row>
-    <row r="91" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S90" s="3"/>
+    </row>
+    <row r="91" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-4409000</v>
+      </c>
+      <c r="E91" s="3">
         <v>-3773000</v>
       </c>
-      <c r="E91" s="3">
+      <c r="F91" s="3">
         <v>-3322000</v>
       </c>
-      <c r="F91" s="3">
+      <c r="G91" s="3">
         <v>-3062000</v>
       </c>
-      <c r="G91" s="3">
+      <c r="H91" s="3">
         <v>-3156000</v>
       </c>
-      <c r="H91" s="3">
+      <c r="I91" s="3">
         <v>-2787000</v>
       </c>
-      <c r="I91" s="3">
+      <c r="J91" s="3">
         <v>-3073000</v>
       </c>
-      <c r="J91" s="3">
+      <c r="K91" s="3">
         <v>-3347000</v>
       </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
         <v>-3717000</v>
       </c>
-      <c r="L91" s="3">
+      <c r="M91" s="3">
         <v>-3384000</v>
       </c>
-      <c r="M91" s="3">
+      <c r="N91" s="3">
         <v>-3314000</v>
       </c>
-      <c r="N91" s="3">
+      <c r="O91" s="3">
         <v>-3736000</v>
       </c>
-      <c r="O91" s="3">
+      <c r="P91" s="3">
         <v>-3848000</v>
       </c>
-      <c r="P91" s="3">
+      <c r="Q91" s="3">
         <v>-4008000</v>
       </c>
-      <c r="Q91" s="3">
+      <c r="R91" s="3">
         <v>-3964000</v>
       </c>
-      <c r="R91" s="3"/>
-    </row>
-    <row r="92" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S91" s="3"/>
+    </row>
+    <row r="92" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -4337,9 +4560,12 @@
       <c r="Q92" s="3">
         <v>0</v>
       </c>
-      <c r="R92" s="3"/>
-    </row>
-    <row r="93" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R92" s="3">
+        <v>0</v>
+      </c>
+      <c r="S92" s="3"/>
+    </row>
+    <row r="93" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -4385,57 +4611,63 @@
       <c r="Q93" s="3">
         <v>0</v>
       </c>
-      <c r="R93" s="3"/>
-    </row>
-    <row r="94" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R93" s="3">
+        <v>0</v>
+      </c>
+      <c r="S93" s="3"/>
+    </row>
+    <row r="94" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-4624000</v>
+      </c>
+      <c r="E94" s="3">
         <v>-3818000</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>-3504000</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>-3500000</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>-4424000</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>-2834000</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>3045000</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>-3490000</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-3511000</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>-5689000</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>-5575000</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>-2891000</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>-4100000</v>
       </c>
-      <c r="P94" s="3">
+      <c r="Q94" s="3">
         <v>-6295000</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="R94" s="3">
         <v>-1093000</v>
       </c>
-      <c r="R94" s="3"/>
-    </row>
-    <row r="95" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S94" s="3"/>
+    </row>
+    <row r="95" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -4454,8 +4686,9 @@
       <c r="P95" s="3"/>
       <c r="Q95" s="3"/>
       <c r="R95" s="3"/>
-    </row>
-    <row r="96" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S95" s="3"/>
+    </row>
+    <row r="96" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -4484,26 +4717,29 @@
         <v>0</v>
       </c>
       <c r="L96" s="3">
+        <v>0</v>
+      </c>
+      <c r="M96" s="3">
         <v>-7236000</v>
       </c>
-      <c r="M96" s="3">
+      <c r="N96" s="3">
         <v>-7436000</v>
       </c>
-      <c r="N96" s="3">
+      <c r="O96" s="3">
         <v>-7287000</v>
       </c>
-      <c r="O96" s="3">
+      <c r="P96" s="3">
         <v>-6911000</v>
       </c>
-      <c r="P96" s="3">
+      <c r="Q96" s="3">
         <v>-6519000</v>
       </c>
-      <c r="Q96" s="3">
+      <c r="R96" s="3">
         <v>-6139000</v>
       </c>
-      <c r="R96" s="3"/>
-    </row>
-    <row r="97" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S96" s="3"/>
+    </row>
+    <row r="97" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -4549,9 +4785,12 @@
       <c r="Q97" s="3">
         <v>0</v>
       </c>
-      <c r="R97" s="3"/>
-    </row>
-    <row r="98" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R97" s="3">
+        <v>0</v>
+      </c>
+      <c r="S97" s="3"/>
+    </row>
+    <row r="98" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -4597,9 +4836,12 @@
       <c r="Q98" s="3">
         <v>0</v>
       </c>
-      <c r="R98" s="3"/>
-    </row>
-    <row r="99" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R98" s="3">
+        <v>0</v>
+      </c>
+      <c r="S98" s="3"/>
+    </row>
+    <row r="99" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -4645,151 +4887,163 @@
       <c r="Q99" s="3">
         <v>0</v>
       </c>
-      <c r="R99" s="3"/>
-    </row>
-    <row r="100" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R99" s="3">
+        <v>0</v>
+      </c>
+      <c r="S99" s="3"/>
+    </row>
+    <row r="100" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>-14460000</v>
+      </c>
+      <c r="E100" s="3">
         <v>-14036000</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>-14855000</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>-12146000</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>-14876000</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>-21531000</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>-8367000</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>-9994000</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>-14375000</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>-8568000</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>-9213000</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>-13019000</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>-7279000</v>
       </c>
-      <c r="P100" s="3">
+      <c r="Q100" s="3">
         <v>-7071000</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="R100" s="3">
         <v>-10410000</v>
       </c>
-      <c r="R100" s="3"/>
-    </row>
-    <row r="101" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S100" s="3"/>
+    </row>
+    <row r="101" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
       <c r="D101" s="3">
+        <v>-86000</v>
+      </c>
+      <c r="E101" s="3">
         <v>112000</v>
       </c>
-      <c r="E101" s="3">
+      <c r="F101" s="3">
         <v>-251000</v>
       </c>
-      <c r="F101" s="3">
+      <c r="G101" s="3">
         <v>-170000</v>
       </c>
-      <c r="G101" s="3">
+      <c r="H101" s="3">
         <v>-497000</v>
       </c>
-      <c r="H101" s="3">
+      <c r="I101" s="3">
         <v>101000</v>
       </c>
-      <c r="I101" s="3">
+      <c r="J101" s="3">
         <v>-139000</v>
       </c>
-      <c r="J101" s="3">
+      <c r="K101" s="3">
         <v>-88000</v>
       </c>
-      <c r="K101" s="3">
+      <c r="L101" s="3">
         <v>19000</v>
       </c>
-      <c r="L101" s="3">
+      <c r="M101" s="3">
         <v>-29000</v>
       </c>
-      <c r="M101" s="3">
+      <c r="N101" s="3">
         <v>-381000</v>
       </c>
-      <c r="N101" s="3">
+      <c r="O101" s="3">
         <v>-411000</v>
       </c>
-      <c r="O101" s="3">
+      <c r="P101" s="3">
         <v>39000</v>
       </c>
-      <c r="P101" s="3">
+      <c r="Q101" s="3">
         <v>4000</v>
       </c>
-      <c r="Q101" s="3">
+      <c r="R101" s="3">
         <v>-113000</v>
       </c>
-      <c r="R101" s="3"/>
-    </row>
-    <row r="102" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S101" s="3"/>
+    </row>
+    <row r="102" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>386000</v>
+      </c>
+      <c r="E102" s="3">
         <v>75000</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>1236000</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>1032000</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>-3074000</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>-5893000</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>11942000</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>1670000</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>-3000000</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>-1533000</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>266000</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>-1713000</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>2618000</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>1511000</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>1668000</v>
       </c>
-      <c r="R102" s="3"/>
+      <c r="S102" s="3"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
